--- a/ORGANOLEPTICO_EFILA.xlsx
+++ b/ORGANOLEPTICO_EFILA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\JUPYTERL\CAPA ORGANOLEPTICO\efila\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\JUPYTERL\ORGANOLEPTICO\efila\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BDC71A4-1A64-4F18-8EDC-805ED39FEA11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE89794D-0DC0-4D0E-ACF3-39740A2F96B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7910" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DFDFD" sheetId="6" r:id="rId1"/>
@@ -830,7 +830,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -861,7 +861,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -933,6 +932,126 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -943,7 +1062,127 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -953,245 +1192,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1584,508 +1595,508 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:P52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.40625" defaultRowHeight="14.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.1328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.6796875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="2.26953125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="2.40625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="2.54296875" style="1" customWidth="1"/>
-    <col min="7" max="8" width="2.40625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="2.54296875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="1.1328125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.86328125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="12.26953125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.86328125" style="1" customWidth="1"/>
-    <col min="14" max="16" width="5.26953125" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="11.40625" style="1"/>
+    <col min="1" max="1" width="11.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="2.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="2.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="2.5703125" style="1" customWidth="1"/>
+    <col min="7" max="8" width="2.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="2.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="1.140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" customWidth="1"/>
+    <col min="14" max="16" width="5.28515625" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.5" thickBot="1">
-      <c r="A1" s="89"/>
-      <c r="B1" s="90"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="80" t="s">
+    <row r="1" spans="1:16" ht="15.75" thickBot="1">
+      <c r="A1" s="126"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="117" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="81"/>
-      <c r="M1" s="29" t="s">
+      <c r="E1" s="117"/>
+      <c r="F1" s="117"/>
+      <c r="G1" s="117"/>
+      <c r="H1" s="117"/>
+      <c r="I1" s="117"/>
+      <c r="J1" s="117"/>
+      <c r="K1" s="117"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="N1" s="73" t="s">
+      <c r="N1" s="110" t="s">
         <v>85</v>
       </c>
-      <c r="O1" s="74"/>
-      <c r="P1" s="75"/>
-    </row>
-    <row r="2" spans="1:16" ht="15.5" thickBot="1">
-      <c r="A2" s="92"/>
-      <c r="B2" s="93"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="82" t="s">
+      <c r="O1" s="111"/>
+      <c r="P1" s="112"/>
+    </row>
+    <row r="2" spans="1:16" ht="15.75" thickBot="1">
+      <c r="A2" s="129"/>
+      <c r="B2" s="130"/>
+      <c r="C2" s="131"/>
+      <c r="D2" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="29" t="s">
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="N2" s="76" t="s">
+      <c r="N2" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="O2" s="77"/>
-      <c r="P2" s="78"/>
-    </row>
-    <row r="3" spans="1:16" ht="15.5" thickBot="1">
-      <c r="A3" s="95"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="97"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="85"/>
-      <c r="M3" s="30" t="s">
+      <c r="O2" s="114"/>
+      <c r="P2" s="115"/>
+    </row>
+    <row r="3" spans="1:16" ht="15.75" thickBot="1">
+      <c r="A3" s="132"/>
+      <c r="B3" s="133"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="121"/>
+      <c r="K3" s="121"/>
+      <c r="L3" s="122"/>
+      <c r="M3" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="N3" s="86">
+      <c r="N3" s="123">
         <v>1</v>
       </c>
-      <c r="O3" s="87"/>
-      <c r="P3" s="88"/>
+      <c r="O3" s="124"/>
+      <c r="P3" s="125"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-    </row>
-    <row r="5" spans="1:16" ht="15" customHeight="1">
-      <c r="A5" s="22" t="s">
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
+    </row>
+    <row r="5" spans="1:16" ht="20.25" customHeight="1">
+      <c r="A5" s="142" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="68" t="s">
+      <c r="B5" s="72"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="139" t="s">
         <v>69</v>
       </c>
-      <c r="K5" s="69"/>
-      <c r="L5" s="70"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="66"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="67"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" s="22" t="s">
+      <c r="K5" s="140"/>
+      <c r="L5" s="141"/>
+      <c r="M5" s="116"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="52"/>
+      <c r="P5" s="53"/>
+    </row>
+    <row r="6" spans="1:16" ht="20.25" customHeight="1">
+      <c r="A6" s="142" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="68" t="s">
+      <c r="B6" s="72"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="139" t="s">
         <v>68</v>
       </c>
-      <c r="K6" s="69"/>
-      <c r="L6" s="70"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="66"/>
-      <c r="O6" s="66"/>
-      <c r="P6" s="67"/>
+      <c r="K6" s="140"/>
+      <c r="L6" s="141"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="52"/>
+      <c r="O6" s="52"/>
+      <c r="P6" s="53"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="119" t="s">
+      <c r="A7" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="120"/>
-      <c r="C7" s="120"/>
-      <c r="D7" s="120"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="120"/>
-      <c r="G7" s="120"/>
-      <c r="H7" s="120"/>
-      <c r="I7" s="120"/>
-      <c r="J7" s="120"/>
-      <c r="K7" s="120"/>
-      <c r="L7" s="120"/>
-      <c r="M7" s="120"/>
-      <c r="N7" s="120"/>
-      <c r="O7" s="120"/>
-      <c r="P7" s="123"/>
+      <c r="B7" s="67"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="67"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="67"/>
+      <c r="M7" s="67"/>
+      <c r="N7" s="67"/>
+      <c r="O7" s="67"/>
+      <c r="P7" s="68"/>
     </row>
     <row r="8" spans="1:16" ht="15" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="72"/>
-      <c r="C8" s="124"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="125"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="125"/>
-      <c r="J8" s="125"/>
-      <c r="K8" s="125"/>
-      <c r="L8" s="126"/>
-      <c r="M8" s="24" t="s">
+      <c r="B8" s="65"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="N8" s="124"/>
-      <c r="O8" s="125"/>
-      <c r="P8" s="126"/>
+      <c r="N8" s="69"/>
+      <c r="O8" s="70"/>
+      <c r="P8" s="71"/>
     </row>
     <row r="9" spans="1:16" ht="15" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="72"/>
-      <c r="C9" s="127"/>
-      <c r="D9" s="128"/>
-      <c r="E9" s="128"/>
-      <c r="F9" s="128"/>
-      <c r="G9" s="128"/>
-      <c r="H9" s="128"/>
-      <c r="I9" s="128"/>
-      <c r="J9" s="128"/>
-      <c r="K9" s="128"/>
-      <c r="L9" s="129"/>
-      <c r="M9" s="24" t="s">
+      <c r="B9" s="65"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="73"/>
+      <c r="J9" s="73"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="74"/>
+      <c r="M9" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="N9" s="130"/>
-      <c r="O9" s="131"/>
-      <c r="P9" s="132"/>
+      <c r="N9" s="75"/>
+      <c r="O9" s="76"/>
+      <c r="P9" s="77"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="65"/>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="66"/>
-      <c r="F10" s="66"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="66"/>
-      <c r="I10" s="66"/>
-      <c r="J10" s="66"/>
-      <c r="K10" s="66"/>
-      <c r="L10" s="67"/>
-      <c r="M10" s="24" t="s">
+      <c r="B10" s="51"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="N10" s="65"/>
-      <c r="O10" s="66"/>
-      <c r="P10" s="67"/>
+      <c r="N10" s="51"/>
+      <c r="O10" s="52"/>
+      <c r="P10" s="53"/>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="65"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
-      <c r="J11" s="66"/>
-      <c r="K11" s="66"/>
-      <c r="L11" s="67"/>
-      <c r="M11" s="24" t="s">
+      <c r="B11" s="51"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="53"/>
+      <c r="M11" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="N11" s="133"/>
-      <c r="O11" s="66"/>
-      <c r="P11" s="67"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="52"/>
+      <c r="P11" s="53"/>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="23" t="s">
         <v>63</v>
       </c>
       <c r="B12" s="21"/>
-      <c r="C12" s="71" t="s">
+      <c r="C12" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="72"/>
-      <c r="E12" s="134"/>
-      <c r="F12" s="135"/>
-      <c r="G12" s="135"/>
-      <c r="H12" s="136"/>
-      <c r="I12" s="23" t="s">
+      <c r="D12" s="65"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="J12" s="26"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="27" t="s">
+      <c r="J12" s="25"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="N12" s="137"/>
-      <c r="O12" s="138"/>
-      <c r="P12" s="139"/>
+      <c r="N12" s="58"/>
+      <c r="O12" s="59"/>
+      <c r="P12" s="60"/>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="23" t="s">
         <v>89</v>
       </c>
       <c r="B13" s="15"/>
-      <c r="C13" s="71" t="s">
+      <c r="C13" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="D13" s="72"/>
-      <c r="E13" s="116"/>
-      <c r="F13" s="117"/>
-      <c r="G13" s="117"/>
-      <c r="H13" s="118"/>
-      <c r="I13" s="44" t="s">
+      <c r="D13" s="65"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="63"/>
+      <c r="I13" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="J13" s="45"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="50" t="s">
+      <c r="J13" s="44"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="N13" s="116"/>
-      <c r="O13" s="117"/>
-      <c r="P13" s="118"/>
+      <c r="N13" s="61"/>
+      <c r="O13" s="62"/>
+      <c r="P13" s="63"/>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="23" t="s">
         <v>90</v>
       </c>
       <c r="B14" s="15"/>
-      <c r="C14" s="71" t="s">
+      <c r="C14" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="72"/>
-      <c r="E14" s="116"/>
-      <c r="F14" s="117"/>
-      <c r="G14" s="117"/>
-      <c r="H14" s="118"/>
-      <c r="I14" s="23" t="s">
+      <c r="D14" s="65"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="J14" s="26"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="51" t="s">
+      <c r="J14" s="25"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="N14" s="116"/>
-      <c r="O14" s="117"/>
-      <c r="P14" s="118"/>
+      <c r="N14" s="61"/>
+      <c r="O14" s="62"/>
+      <c r="P14" s="63"/>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" s="119" t="s">
+      <c r="A15" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="120"/>
-      <c r="C15" s="120"/>
-      <c r="D15" s="120"/>
-      <c r="E15" s="120"/>
-      <c r="F15" s="120"/>
-      <c r="G15" s="120"/>
-      <c r="H15" s="120"/>
-      <c r="I15" s="120"/>
-      <c r="J15" s="120"/>
-      <c r="K15" s="120"/>
-      <c r="L15" s="120"/>
-      <c r="M15" s="120"/>
-      <c r="N15" s="120"/>
-      <c r="O15" s="120"/>
-      <c r="P15" s="120"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="67"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="67"/>
+      <c r="K15" s="67"/>
+      <c r="L15" s="67"/>
+      <c r="M15" s="67"/>
+      <c r="N15" s="67"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="67"/>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="68" t="s">
+      <c r="A16" s="88" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="69"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="69"/>
-      <c r="E16" s="69"/>
-      <c r="F16" s="70"/>
-      <c r="G16" s="33" t="s">
+      <c r="B16" s="89"/>
+      <c r="C16" s="89"/>
+      <c r="D16" s="89"/>
+      <c r="E16" s="89"/>
+      <c r="F16" s="90"/>
+      <c r="G16" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="H16" s="33" t="s">
+      <c r="H16" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="I16" s="34" t="s">
+      <c r="I16" s="33" t="s">
         <v>4</v>
       </c>
       <c r="J16" s="2"/>
-      <c r="K16" s="68" t="s">
+      <c r="K16" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="L16" s="69"/>
-      <c r="M16" s="70"/>
-      <c r="N16" s="33" t="s">
+      <c r="L16" s="89"/>
+      <c r="M16" s="90"/>
+      <c r="N16" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="O16" s="33" t="s">
+      <c r="O16" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="P16" s="34" t="s">
+      <c r="P16" s="33" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="27.75" customHeight="1">
-      <c r="A17" s="55" t="s">
+      <c r="A17" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="B17" s="121"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
+      <c r="B17" s="79"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="79"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
       <c r="J17" s="2"/>
       <c r="K17" s="8" t="s">
         <v>6</v>
       </c>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="38"/>
-      <c r="P17" s="38"/>
+      <c r="N17" s="37"/>
+      <c r="O17" s="37"/>
+      <c r="P17" s="37"/>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="52" t="s">
+      <c r="A18" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="B18" s="53"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
+      <c r="B18" s="92"/>
+      <c r="C18" s="92"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="92"/>
+      <c r="F18" s="93"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
       <c r="J18" s="2"/>
       <c r="K18" s="8" t="s">
         <v>7</v>
       </c>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="39"/>
-      <c r="P18" s="39"/>
+      <c r="N18" s="37"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="38"/>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" s="52" t="s">
+      <c r="A19" s="91" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="53"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="54"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="39"/>
+      <c r="B19" s="92"/>
+      <c r="C19" s="92"/>
+      <c r="D19" s="92"/>
+      <c r="E19" s="92"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
       <c r="J19" s="2"/>
       <c r="K19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
-      <c r="N19" s="39"/>
-      <c r="O19" s="38"/>
-      <c r="P19" s="39"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="37"/>
+      <c r="P19" s="38"/>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="106" t="s">
+      <c r="A20" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="107"/>
-      <c r="C20" s="107"/>
-      <c r="D20" s="60" t="s">
+      <c r="B20" s="82"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="61"/>
-      <c r="F20" s="110"/>
-      <c r="G20" s="60" t="s">
+      <c r="E20" s="86"/>
+      <c r="F20" s="87"/>
+      <c r="G20" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="61"/>
-      <c r="I20" s="110"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="87"/>
       <c r="J20" s="2"/>
       <c r="K20" s="11" t="s">
         <v>9</v>
       </c>
       <c r="L20" s="14"/>
       <c r="M20" s="14"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="38"/>
-      <c r="P20" s="39"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="37"/>
+      <c r="P20" s="38"/>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" s="108"/>
-      <c r="B21" s="109"/>
-      <c r="C21" s="109"/>
-      <c r="D21" s="31" t="s">
+      <c r="A21" s="83"/>
+      <c r="B21" s="84"/>
+      <c r="C21" s="84"/>
+      <c r="D21" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="E21" s="31" t="s">
+      <c r="E21" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="F21" s="32" t="s">
+      <c r="F21" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="G21" s="31" t="s">
+      <c r="G21" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="H21" s="31" t="s">
+      <c r="H21" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="I21" s="32" t="s">
+      <c r="I21" s="31" t="s">
         <v>4</v>
       </c>
       <c r="J21" s="2"/>
@@ -2094,44 +2105,44 @@
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="39"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="37"/>
+      <c r="P21" s="38"/>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" s="52" t="s">
+      <c r="A22" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="53"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="38"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
+      <c r="B22" s="92"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="38"/>
       <c r="J22" s="2"/>
       <c r="K22" s="13" t="s">
         <v>13</v>
       </c>
       <c r="L22" s="9"/>
       <c r="M22" s="9"/>
-      <c r="N22" s="39"/>
-      <c r="O22" s="38"/>
-      <c r="P22" s="39"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="37"/>
+      <c r="P22" s="38"/>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" s="55" t="s">
+      <c r="A23" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="39"/>
+      <c r="B23" s="135"/>
+      <c r="C23" s="135"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="38"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
@@ -2139,194 +2150,194 @@
       <c r="N23" s="2"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="52" t="s">
+      <c r="A24" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="B24" s="53"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="39"/>
+      <c r="B24" s="92"/>
+      <c r="C24" s="93"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
       <c r="J24" s="2"/>
-      <c r="K24" s="57" t="s">
+      <c r="K24" s="136" t="s">
         <v>72</v>
       </c>
-      <c r="L24" s="58"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="58"/>
-      <c r="O24" s="58"/>
-      <c r="P24" s="59"/>
+      <c r="L24" s="137"/>
+      <c r="M24" s="137"/>
+      <c r="N24" s="137"/>
+      <c r="O24" s="137"/>
+      <c r="P24" s="138"/>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="52" t="s">
+      <c r="A25" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="53"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="39"/>
+      <c r="B25" s="92"/>
+      <c r="C25" s="92"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="38"/>
       <c r="J25" s="2"/>
-      <c r="K25" s="60" t="s">
+      <c r="K25" s="85" t="s">
         <v>71</v>
       </c>
-      <c r="L25" s="61"/>
-      <c r="M25" s="61"/>
-      <c r="N25" s="33" t="s">
+      <c r="L25" s="86"/>
+      <c r="M25" s="86"/>
+      <c r="N25" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="O25" s="33" t="s">
+      <c r="O25" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="P25" s="34" t="s">
+      <c r="P25" s="33" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="52" t="s">
+      <c r="A26" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="53"/>
-      <c r="C26" s="54"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="39"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="39"/>
-      <c r="K26" s="62" t="s">
+      <c r="B26" s="92"/>
+      <c r="C26" s="93"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="38"/>
+      <c r="K26" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="L26" s="63"/>
-      <c r="M26" s="64"/>
-      <c r="N26" s="41"/>
-      <c r="O26" s="40"/>
-      <c r="P26" s="38"/>
+      <c r="L26" s="105"/>
+      <c r="M26" s="106"/>
+      <c r="N26" s="40"/>
+      <c r="O26" s="39"/>
+      <c r="P26" s="37"/>
     </row>
     <row r="27" spans="1:16" ht="23.25" customHeight="1">
-      <c r="A27" s="103" t="s">
+      <c r="A27" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="104"/>
-      <c r="C27" s="105"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="39"/>
-      <c r="K27" s="111" t="s">
+      <c r="B27" s="100"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="38"/>
+      <c r="K27" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="L27" s="112"/>
-      <c r="M27" s="112"/>
-      <c r="N27" s="41"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="38"/>
+      <c r="L27" s="103"/>
+      <c r="M27" s="103"/>
+      <c r="N27" s="40"/>
+      <c r="O27" s="39"/>
+      <c r="P27" s="37"/>
     </row>
     <row r="28" spans="1:16" ht="23.25" customHeight="1">
-      <c r="A28" s="98" t="s">
+      <c r="A28" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="99"/>
-      <c r="C28" s="99"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="39"/>
+      <c r="B28" s="95"/>
+      <c r="C28" s="95"/>
+      <c r="D28" s="38"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="38"/>
       <c r="K28" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="41"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="38"/>
+      <c r="N28" s="40"/>
+      <c r="O28" s="39"/>
+      <c r="P28" s="37"/>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="98" t="s">
+      <c r="A29" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="99"/>
-      <c r="C29" s="99"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="38"/>
-      <c r="K29" s="62" t="s">
+      <c r="B29" s="95"/>
+      <c r="C29" s="95"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="37"/>
+      <c r="K29" s="104" t="s">
         <v>22</v>
       </c>
-      <c r="L29" s="63"/>
-      <c r="M29" s="64"/>
-      <c r="N29" s="41"/>
-      <c r="O29" s="40"/>
-      <c r="P29" s="38"/>
+      <c r="L29" s="105"/>
+      <c r="M29" s="106"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="37"/>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" s="106" t="s">
+      <c r="A30" s="81" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="107"/>
-      <c r="C30" s="107"/>
-      <c r="D30" s="60" t="s">
+      <c r="B30" s="82"/>
+      <c r="C30" s="82"/>
+      <c r="D30" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="E30" s="61"/>
-      <c r="F30" s="110"/>
-      <c r="G30" s="60" t="s">
+      <c r="E30" s="86"/>
+      <c r="F30" s="87"/>
+      <c r="G30" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="61"/>
-      <c r="I30" s="110"/>
+      <c r="H30" s="86"/>
+      <c r="I30" s="87"/>
       <c r="K30" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="N30" s="41"/>
-      <c r="O30" s="40"/>
-      <c r="P30" s="38"/>
+      <c r="N30" s="40"/>
+      <c r="O30" s="39"/>
+      <c r="P30" s="37"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="108"/>
-      <c r="B31" s="109"/>
-      <c r="C31" s="109"/>
-      <c r="D31" s="33" t="s">
+      <c r="A31" s="83"/>
+      <c r="B31" s="84"/>
+      <c r="C31" s="84"/>
+      <c r="D31" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="E31" s="33" t="s">
+      <c r="E31" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="F31" s="34" t="s">
+      <c r="F31" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="G31" s="33" t="s">
+      <c r="G31" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="H31" s="33" t="s">
+      <c r="H31" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="I31" s="34" t="s">
+      <c r="I31" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="K31" s="23" t="s">
+      <c r="K31" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="L31" s="47"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="33" t="s">
+      <c r="L31" s="46"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="O31" s="33" t="s">
+      <c r="O31" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="P31" s="34" t="s">
+      <c r="P31" s="33" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2336,18 +2347,18 @@
       </c>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
-      <c r="D32" s="38"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="39"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="38"/>
       <c r="K32" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="N32" s="41"/>
-      <c r="O32" s="48"/>
-      <c r="P32" s="38"/>
+      <c r="N32" s="40"/>
+      <c r="O32" s="47"/>
+      <c r="P32" s="37"/>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" s="11" t="s">
@@ -2355,20 +2366,20 @@
       </c>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
-      <c r="D33" s="38"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="38"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="39"/>
-      <c r="K33" s="62" t="s">
+      <c r="D33" s="37"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="38"/>
+      <c r="K33" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="L33" s="63"/>
-      <c r="M33" s="63"/>
-      <c r="N33" s="41"/>
-      <c r="O33" s="48"/>
-      <c r="P33" s="38"/>
+      <c r="L33" s="105"/>
+      <c r="M33" s="105"/>
+      <c r="N33" s="40"/>
+      <c r="O33" s="47"/>
+      <c r="P33" s="37"/>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" s="11" t="s">
@@ -2376,18 +2387,18 @@
       </c>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="39"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="38"/>
       <c r="K34" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="N34" s="41"/>
-      <c r="O34" s="49"/>
-      <c r="P34" s="38"/>
+      <c r="N34" s="40"/>
+      <c r="O34" s="48"/>
+      <c r="P34" s="37"/>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" s="8" t="s">
@@ -2395,24 +2406,24 @@
       </c>
       <c r="B35" s="7"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="38"/>
-      <c r="K35" s="60" t="s">
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="37"/>
+      <c r="K35" s="85" t="s">
         <v>78</v>
       </c>
-      <c r="L35" s="61"/>
-      <c r="M35" s="61"/>
-      <c r="N35" s="33" t="s">
+      <c r="L35" s="86"/>
+      <c r="M35" s="86"/>
+      <c r="N35" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="O35" s="33" t="s">
+      <c r="O35" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="P35" s="34" t="s">
+      <c r="P35" s="33" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2422,20 +2433,20 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="39"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
       <c r="K36" s="13" t="s">
         <v>31</v>
       </c>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
-      <c r="N36" s="41"/>
-      <c r="O36" s="41"/>
-      <c r="P36" s="38"/>
+      <c r="N36" s="40"/>
+      <c r="O36" s="40"/>
+      <c r="P36" s="37"/>
     </row>
     <row r="37" spans="1:16">
       <c r="A37" s="11" t="s">
@@ -2443,20 +2454,20 @@
       </c>
       <c r="B37" s="10"/>
       <c r="C37" s="10"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="39"/>
-      <c r="H37" s="39"/>
-      <c r="I37" s="38"/>
-      <c r="K37" s="62" t="s">
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="37"/>
+      <c r="K37" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="L37" s="63"/>
-      <c r="M37" s="64"/>
-      <c r="N37" s="41"/>
-      <c r="O37" s="42"/>
-      <c r="P37" s="38"/>
+      <c r="L37" s="105"/>
+      <c r="M37" s="106"/>
+      <c r="N37" s="40"/>
+      <c r="O37" s="41"/>
+      <c r="P37" s="37"/>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="8" t="s">
@@ -2464,47 +2475,47 @@
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="38"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="38"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="39"/>
-      <c r="K38" s="60" t="s">
+      <c r="D38" s="37"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="37"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="38"/>
+      <c r="K38" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="L38" s="61"/>
-      <c r="M38" s="61"/>
-      <c r="N38" s="33" t="s">
+      <c r="L38" s="86"/>
+      <c r="M38" s="86"/>
+      <c r="N38" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="O38" s="33" t="s">
+      <c r="O38" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="P38" s="34" t="s">
+      <c r="P38" s="33" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="21.75" customHeight="1">
-      <c r="A39" s="98" t="s">
+      <c r="A39" s="94" t="s">
         <v>49</v>
       </c>
-      <c r="B39" s="99"/>
-      <c r="C39" s="100"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="38"/>
-      <c r="H39" s="39"/>
-      <c r="I39" s="39"/>
-      <c r="K39" s="113" t="s">
+      <c r="B39" s="95"/>
+      <c r="C39" s="96"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="37"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="38"/>
+      <c r="K39" s="107" t="s">
         <v>36</v>
       </c>
-      <c r="L39" s="114"/>
-      <c r="M39" s="115"/>
-      <c r="N39" s="41"/>
-      <c r="O39" s="38"/>
-      <c r="P39" s="38"/>
+      <c r="L39" s="108"/>
+      <c r="M39" s="109"/>
+      <c r="N39" s="40"/>
+      <c r="O39" s="37"/>
+      <c r="P39" s="37"/>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" s="13" t="s">
@@ -2512,12 +2523,12 @@
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="39"/>
-      <c r="G40" s="39"/>
-      <c r="H40" s="39"/>
-      <c r="I40" s="39"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="38"/>
       <c r="K40" s="18"/>
       <c r="L40" s="5"/>
       <c r="M40" s="5"/>
@@ -2531,12 +2542,12 @@
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
-      <c r="D41" s="38"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="38"/>
-      <c r="H41" s="39"/>
-      <c r="I41" s="39"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="38"/>
       <c r="K41" s="16" t="s">
         <v>42</v>
       </c>
@@ -2549,12 +2560,12 @@
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="39"/>
-      <c r="F42" s="39"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="39"/>
-      <c r="I42" s="39"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="38"/>
+      <c r="I42" s="38"/>
       <c r="O42" s="5"/>
       <c r="P42" s="5"/>
     </row>
@@ -2564,16 +2575,16 @@
       </c>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="39"/>
-      <c r="I43" s="39"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
       <c r="K43" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="N43" s="39"/>
+      <c r="N43" s="38"/>
     </row>
     <row r="44" spans="1:16">
       <c r="A44" s="13" t="s">
@@ -2581,12 +2592,12 @@
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
-      <c r="D44" s="38"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="38"/>
-      <c r="H44" s="39"/>
-      <c r="I44" s="38"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="37"/>
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="17" t="s">
@@ -2643,10 +2654,10 @@
       <c r="G49" s="10"/>
       <c r="H49" s="10"/>
       <c r="I49" s="10"/>
-      <c r="L49" s="101" t="s">
+      <c r="L49" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="M49" s="101"/>
+      <c r="M49" s="97"/>
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="5"/>
@@ -2660,38 +2671,33 @@
       <c r="I50" s="5"/>
     </row>
     <row r="52" spans="1:13">
-      <c r="L52" s="102"/>
-      <c r="M52" s="102"/>
+      <c r="L52" s="98"/>
+      <c r="M52" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B11:L11"/>
-    <mergeCell ref="N11:P11"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="N12:P12"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="B10:L10"/>
-    <mergeCell ref="N10:P10"/>
-    <mergeCell ref="A7:P7"/>
-    <mergeCell ref="C8:L8"/>
-    <mergeCell ref="N8:P8"/>
-    <mergeCell ref="C9:L9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="A15:P15"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A20:C21"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="K24:P24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="B6:I6"/>
+    <mergeCell ref="J6:L6"/>
+    <mergeCell ref="M6:P6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="B5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="D1:L1"/>
+    <mergeCell ref="D2:L3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="A1:C3"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="L49:M49"/>
     <mergeCell ref="L52:M52"/>
@@ -2708,28 +2714,33 @@
     <mergeCell ref="K37:M37"/>
     <mergeCell ref="K38:M38"/>
     <mergeCell ref="K39:M39"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="M5:P5"/>
-    <mergeCell ref="D1:L1"/>
-    <mergeCell ref="D2:L3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="J6:L6"/>
-    <mergeCell ref="M6:P6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="K24:P24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="A15:P15"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="B10:L10"/>
+    <mergeCell ref="N10:P10"/>
+    <mergeCell ref="A7:P7"/>
+    <mergeCell ref="C8:L8"/>
+    <mergeCell ref="N8:P8"/>
+    <mergeCell ref="C9:L9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="B11:L11"/>
+    <mergeCell ref="N11:P11"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="N12:P12"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.12" top="0.75" bottom="0.44" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="99" orientation="portrait" r:id="rId1"/>
